--- a/data/excel/supermercados.xlsx
+++ b/data/excel/supermercados.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -509,11 +509,11 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>103.711315881602</v>
+        <v>103.715091331918</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>99.250870525954</v>
+        <v>99.235038570369</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
@@ -535,16 +535,16 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>99.2028083543713</v>
+        <v>99.20056844787069</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.347170305290177</v>
+        <v>-4.352811944791668</v>
       </c>
       <c r="G3" t="n">
-        <v>99.1013672210494</v>
+        <v>99.0923809065888</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1506317316032977</v>
+        <v>-0.1437573520758377</v>
       </c>
       <c r="I3" t="n">
         <v>25994.2001680691</v>
@@ -565,16 +565,16 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>96.3678018543402</v>
+        <v>96.359589014444</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.857788551614306</v>
+        <v>-2.863874146970858</v>
       </c>
       <c r="G4" t="n">
-        <v>99.00239007340291</v>
+        <v>98.99982264079181</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.09987465402542739</v>
+        <v>-0.09340603682159099</v>
       </c>
       <c r="I4" t="n">
         <v>27780.00652224732</v>
@@ -595,16 +595,16 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>98.6994020077093</v>
+        <v>98.69998768692049</v>
       </c>
       <c r="F5" t="n">
-        <v>2.419480478441642</v>
+        <v>2.428817615780488</v>
       </c>
       <c r="G5" t="n">
-        <v>98.9570203130302</v>
+        <v>98.9624693962575</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04582693441953722</v>
+        <v>-0.03773061762932173</v>
       </c>
       <c r="I5" t="n">
         <v>29134.27222061001</v>
@@ -625,16 +625,16 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>98.4076228430696</v>
+        <v>98.4140297315748</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2956240450341312</v>
+        <v>-0.289724408327956</v>
       </c>
       <c r="G6" t="n">
-        <v>99.0179092992034</v>
+        <v>99.03201827649259</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06153073928518893</v>
+        <v>0.07027803637014074</v>
       </c>
       <c r="I6" t="n">
         <v>27969.00467693989</v>
@@ -655,16 +655,16 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>98.320700294451</v>
+        <v>98.3037047262535</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.08832908072295709</v>
+        <v>-0.1121029243718681</v>
       </c>
       <c r="G7" t="n">
-        <v>99.2725526394798</v>
+        <v>99.2934017657645</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2571689728440418</v>
+        <v>0.2639383644006443</v>
       </c>
       <c r="I7" t="n">
         <v>29132.712745602</v>
@@ -685,16 +685,16 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>99.6181154591102</v>
+        <v>99.6266862106479</v>
       </c>
       <c r="F8" t="n">
-        <v>1.319574780055149</v>
+        <v>1.345810402648112</v>
       </c>
       <c r="G8" t="n">
-        <v>99.7711401561648</v>
+        <v>99.79374483225619</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5022410559902539</v>
+        <v>0.5039036407192583</v>
       </c>
       <c r="I8" t="n">
         <v>31182.30245559271</v>
@@ -715,16 +715,16 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>100.590392421793</v>
+        <v>100.59930802086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9760041717330949</v>
+        <v>0.9762663471066304</v>
       </c>
       <c r="G9" t="n">
-        <v>100.455164430733</v>
+        <v>100.473361115842</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6855933223751407</v>
+        <v>0.6810209244358703</v>
       </c>
       <c r="I9" t="n">
         <v>31154.8809417369</v>
@@ -745,16 +745,16 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>102.172005458306</v>
+        <v>102.167035289943</v>
       </c>
       <c r="F10" t="n">
-        <v>1.572330118646946</v>
+        <v>1.558387726442348</v>
       </c>
       <c r="G10" t="n">
-        <v>101.173598684613</v>
+        <v>101.183605155113</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7151790133949447</v>
+        <v>0.7068978596745978</v>
       </c>
       <c r="I10" t="n">
         <v>30521.50619627021</v>
@@ -775,16 +775,16 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>102.629510439151</v>
+        <v>102.627375967895</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4477791923460899</v>
+        <v>0.4505765256333376</v>
       </c>
       <c r="G11" t="n">
-        <v>101.791467952653</v>
+        <v>101.791850454304</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6107020765032445</v>
+        <v>0.6011302900885767</v>
       </c>
       <c r="I11" t="n">
         <v>32445.98301393</v>
@@ -805,16 +805,16 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>103.261569392945</v>
+        <v>103.280167341253</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6158647265191348</v>
+        <v>0.6360791817986495</v>
       </c>
       <c r="G12" t="n">
-        <v>102.211575683975</v>
+        <v>102.20379089238</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4127140906518889</v>
+        <v>0.4046890161024379</v>
       </c>
       <c r="I12" t="n">
         <v>33628.98265709631</v>
@@ -835,16 +835,16 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>98.16930380106049</v>
+        <v>98.15307740231189</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.931423783137305</v>
+        <v>-4.964254097304504</v>
       </c>
       <c r="G13" t="n">
-        <v>102.394502363587</v>
+        <v>102.382292017943</v>
       </c>
       <c r="H13" t="n">
-        <v>0.178968652413289</v>
+        <v>0.1746521572286497</v>
       </c>
       <c r="I13" t="n">
         <v>40766.3221043007</v>
@@ -869,16 +869,16 @@
         <v>-2.695173520247129</v>
       </c>
       <c r="E14" t="n">
-        <v>100.727907489735</v>
+        <v>100.744111404699</v>
       </c>
       <c r="F14" t="n">
-        <v>2.606317443036474</v>
+        <v>2.639788859361914</v>
       </c>
       <c r="G14" t="n">
-        <v>102.348953147993</v>
+        <v>102.335846590093</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.04448404410644002</v>
+        <v>-0.04536470803159887</v>
       </c>
       <c r="I14" t="n">
         <v>32479.20800557399</v>
@@ -907,16 +907,16 @@
         <v>-0.5944912143364234</v>
       </c>
       <c r="E15" t="n">
-        <v>100.858201040917</v>
+        <v>100.855195156971</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1293519883705159</v>
+        <v>0.1102632706995337</v>
       </c>
       <c r="G15" t="n">
-        <v>102.102520192566</v>
+        <v>102.091560889852</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2407772115369511</v>
+        <v>-0.2387098053915366</v>
       </c>
       <c r="I15" t="n">
         <v>31736.82455214001</v>
@@ -945,16 +945,16 @@
         <v>2.782517121744021</v>
       </c>
       <c r="E16" t="n">
-        <v>101.136028248281</v>
+        <v>101.130448721516</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2754631794902735</v>
+        <v>0.2729195696033173</v>
       </c>
       <c r="G16" t="n">
-        <v>101.677455574816</v>
+        <v>101.670140687654</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4163115826605832</v>
+        <v>-0.4127865207709789</v>
       </c>
       <c r="I16" t="n">
         <v>36531.29132866998</v>
@@ -983,16 +983,16 @@
         <v>1.492074168512048</v>
       </c>
       <c r="E17" t="n">
-        <v>101.647335601569</v>
+        <v>101.647001475393</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5055640033962732</v>
+        <v>0.5107786630112088</v>
       </c>
       <c r="G17" t="n">
-        <v>101.06058329654</v>
+        <v>101.058267428671</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6066952352304753</v>
+        <v>-0.6018219851418962</v>
       </c>
       <c r="I17" t="n">
         <v>34113.74566680001</v>
@@ -1021,16 +1021,16 @@
         <v>1.80805939712072</v>
       </c>
       <c r="E18" t="n">
-        <v>100.888855996981</v>
+        <v>100.886134518486</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7461873939923436</v>
+        <v>-0.74853851649641</v>
       </c>
       <c r="G18" t="n">
-        <v>100.21997394844</v>
+        <v>100.222167934358</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8317875483000279</v>
+        <v>-0.8273439824239404</v>
       </c>
       <c r="I18" t="n">
         <v>35133.14639127501</v>
@@ -1059,16 +1059,16 @@
         <v>2.202687587763652</v>
       </c>
       <c r="E19" t="n">
-        <v>100.08710996398</v>
+        <v>100.083952484102</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.794682450383803</v>
+        <v>-0.7951360592936823</v>
       </c>
       <c r="G19" t="n">
-        <v>99.1243054301713</v>
+        <v>99.12889132761239</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.09326362311009</v>
+        <v>-1.090853080988694</v>
       </c>
       <c r="I19" t="n">
         <v>38338.20974565649</v>
@@ -1097,16 +1097,16 @@
         <v>1.450289934539484</v>
       </c>
       <c r="E20" t="n">
-        <v>99.1529318197661</v>
+        <v>99.14647342435271</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9333650902200077</v>
+        <v>-0.9366926829735434</v>
       </c>
       <c r="G20" t="n">
-        <v>97.78061080565131</v>
+        <v>97.78482214654559</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.355565235679322</v>
+        <v>-1.355880372579549</v>
       </c>
       <c r="I20" t="n">
         <v>39278.44996264218</v>
@@ -1135,16 +1135,16 @@
         <v>0.7357230212850396</v>
       </c>
       <c r="E21" t="n">
-        <v>96.4336719346862</v>
+        <v>96.4269019935914</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.742490650728101</v>
+        <v>-2.742983524105171</v>
       </c>
       <c r="G21" t="n">
-        <v>96.2451700001364</v>
+        <v>96.24661068514</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.570291689593503</v>
+        <v>-1.573057482377322</v>
       </c>
       <c r="I21" t="n">
         <v>39491.90727419412</v>
@@ -1173,16 +1173,16 @@
         <v>-0.2187102933078999</v>
       </c>
       <c r="E22" t="n">
-        <v>93.94867758406509</v>
+        <v>93.9546846750812</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.576894875790032</v>
+        <v>-2.563825309532916</v>
       </c>
       <c r="G22" t="n">
-        <v>94.6233694231165</v>
+        <v>94.6205060128831</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.685072172471209</v>
+        <v>-1.68951889389281</v>
       </c>
       <c r="I22" t="n">
         <v>39925.54899754219</v>
@@ -1211,16 +1211,16 @@
         <v>-1.226499475666143</v>
       </c>
       <c r="E23" t="n">
-        <v>92.5118941717392</v>
+        <v>92.5223227808482</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.529327979140803</v>
+        <v>-1.52452418864101</v>
       </c>
       <c r="G23" t="n">
-        <v>93.03900547752509</v>
+        <v>93.032169473663</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.674389693846962</v>
+        <v>-1.678638813243964</v>
       </c>
       <c r="I23" t="n">
         <v>43420.25382248798</v>
@@ -1249,16 +1249,16 @@
         <v>-2.302905169367886</v>
       </c>
       <c r="E24" t="n">
-        <v>90.52740951475479</v>
+        <v>90.5221233508929</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.145112987634221</v>
+        <v>-2.161856047100159</v>
       </c>
       <c r="G24" t="n">
-        <v>91.59451862114599</v>
+        <v>91.5860156802854</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.552560508321463</v>
+        <v>-1.554466376049632</v>
       </c>
       <c r="I24" t="n">
         <v>44849.44600603298</v>
@@ -1287,16 +1287,16 @@
         <v>-2.958552119227154</v>
       </c>
       <c r="E25" t="n">
-        <v>90.286237239766</v>
+        <v>90.29693045740579</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2664080152978414</v>
+        <v>-0.2487711126861143</v>
       </c>
       <c r="G25" t="n">
-        <v>90.35051457560439</v>
+        <v>90.34254180473791</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.358164292218262</v>
+        <v>-1.357711509023702</v>
       </c>
       <c r="I25" t="n">
         <v>57203.95586361999</v>
@@ -1325,16 +1325,16 @@
         <v>-10.65208314640479</v>
       </c>
       <c r="E26" t="n">
-        <v>89.1253725583128</v>
+        <v>89.1339015000062</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.285760395984141</v>
+        <v>-1.288004975925745</v>
       </c>
       <c r="G26" t="n">
-        <v>89.33384822782671</v>
+        <v>89.32849224484249</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.125246881606799</v>
+        <v>-1.12244966727539</v>
       </c>
       <c r="I26" t="n">
         <v>45433.623712056</v>
@@ -1363,16 +1363,16 @@
         <v>-11.37039679719246</v>
       </c>
       <c r="E27" t="n">
-        <v>88.49723517962531</v>
+        <v>88.48994038051011</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.7047795264771679</v>
+        <v>-0.7224648631542863</v>
       </c>
       <c r="G27" t="n">
-        <v>88.5317960598566</v>
+        <v>88.5253328189377</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8978144162385604</v>
+        <v>-0.8991077826584188</v>
       </c>
       <c r="I27" t="n">
         <v>44592.14489534219</v>
@@ -1401,16 +1401,16 @@
         <v>-12.50176711185951</v>
       </c>
       <c r="E28" t="n">
-        <v>87.8481134771923</v>
+        <v>87.84092942102821</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7334937652181566</v>
+        <v>-0.7334290843582068</v>
       </c>
       <c r="G28" t="n">
-        <v>87.91979250987239</v>
+        <v>87.9057459178162</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6912810732659551</v>
+        <v>-0.6998978500185302</v>
       </c>
       <c r="I28" t="n">
         <v>51065.69425464903</v>
@@ -1439,16 +1439,16 @@
         <v>-12.54970728794652</v>
       </c>
       <c r="E29" t="n">
-        <v>87.27000867959229</v>
+        <v>87.26985327739401</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6580730931121224</v>
+        <v>-0.6501253429332365</v>
       </c>
       <c r="G29" t="n">
-        <v>87.4765415710946</v>
+        <v>87.4508543168099</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5041537589252414</v>
+        <v>-0.5174765269969868</v>
       </c>
       <c r="I29" t="n">
         <v>49621.40927512204</v>
@@ -1477,16 +1477,16 @@
         <v>-12.74465163267955</v>
       </c>
       <c r="E30" t="n">
-        <v>87.2372226641041</v>
+        <v>87.219686053026</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.03756847969222576</v>
+        <v>-0.05748517097714512</v>
       </c>
       <c r="G30" t="n">
-        <v>87.18974132163019</v>
+        <v>87.1526784017678</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3278596116323484</v>
+        <v>-0.3409639818518997</v>
       </c>
       <c r="I30" t="n">
         <v>50778.29991440001</v>
@@ -1515,16 +1515,16 @@
         <v>-12.84496235491217</v>
       </c>
       <c r="E31" t="n">
-        <v>86.63301710632081</v>
+        <v>86.63690158143289</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6926006346049149</v>
+        <v>-0.6681799694151493</v>
       </c>
       <c r="G31" t="n">
-        <v>87.0352519990184</v>
+        <v>86.9917848375856</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1771874996645693</v>
+        <v>-0.1846111526722041</v>
       </c>
       <c r="I31" t="n">
         <v>54413.41961482001</v>
@@ -1553,16 +1553,16 @@
         <v>-12.83485090738809</v>
       </c>
       <c r="E32" t="n">
-        <v>86.7167390052072</v>
+        <v>86.72187511056261</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09663971275945471</v>
+        <v>0.09808006470525754</v>
       </c>
       <c r="G32" t="n">
-        <v>86.98439658701081</v>
+        <v>86.9427926279281</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.05843082066122918</v>
+        <v>-0.05631820263140241</v>
       </c>
       <c r="I32" t="n">
         <v>55044.48225731951</v>
@@ -1591,16 +1591,16 @@
         <v>-12.16743408468131</v>
       </c>
       <c r="E33" t="n">
-        <v>87.9861929230462</v>
+        <v>87.99460922762719</v>
       </c>
       <c r="F33" t="n">
-        <v>1.463908735962477</v>
+        <v>1.467604471699872</v>
       </c>
       <c r="G33" t="n">
-        <v>86.9936430462852</v>
+        <v>86.96138092099051</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0106300205981853</v>
+        <v>0.02137991258453553</v>
       </c>
       <c r="I33" t="n">
         <v>59672.10445566601</v>
@@ -1629,16 +1629,16 @@
         <v>-11.83634519096635</v>
       </c>
       <c r="E34" t="n">
-        <v>88.28755428730641</v>
+        <v>88.2865969013078</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3425098350644333</v>
+        <v>0.3318245018001988</v>
       </c>
       <c r="G34" t="n">
-        <v>87.0250637616126</v>
+        <v>87.00514552051069</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03611840385933363</v>
+        <v>0.0503264771749059</v>
       </c>
       <c r="I34" t="n">
         <v>57885.30640686599</v>
@@ -1667,16 +1667,16 @@
         <v>-10.85120481050128</v>
       </c>
       <c r="E35" t="n">
-        <v>90.7495375170672</v>
+        <v>90.7527626275524</v>
       </c>
       <c r="F35" t="n">
-        <v>2.788596025379732</v>
+        <v>2.793363673312072</v>
       </c>
       <c r="G35" t="n">
-        <v>87.0524236016176</v>
+        <v>87.0433585931909</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0314390347129887</v>
+        <v>0.04392047441746172</v>
       </c>
       <c r="I35" t="n">
         <v>66325.57959367818</v>
@@ -1705,16 +1705,16 @@
         <v>-10.13165068365319</v>
       </c>
       <c r="E36" t="n">
-        <v>86.18769343097949</v>
+        <v>86.194470487826</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.026851057207608</v>
+        <v>-5.022758545030243</v>
       </c>
       <c r="G36" t="n">
-        <v>87.05651920921019</v>
+        <v>87.0531648245901</v>
       </c>
       <c r="H36" t="n">
-        <v>0.004704759986154272</v>
+        <v>0.01126591569729385</v>
       </c>
       <c r="I36" t="n">
         <v>67943.71018742798</v>
@@ -1743,16 +1743,16 @@
         <v>-9.767413595753805</v>
       </c>
       <c r="E37" t="n">
-        <v>86.2005264428339</v>
+        <v>86.1986340139957</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01488961050417004</v>
+        <v>0.004830386620085392</v>
       </c>
       <c r="G37" t="n">
-        <v>87.05047216709821</v>
+        <v>87.0469876213494</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.006946110603678335</v>
+        <v>-0.007095897378505356</v>
       </c>
       <c r="I37" t="n">
         <v>83524.644291502</v>
@@ -1781,16 +1781,16 @@
         <v>-1.696952732915169</v>
       </c>
       <c r="E38" t="n">
-        <v>86.8339883413724</v>
+        <v>86.828218435694</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7348701042546395</v>
+        <v>0.7303879335211576</v>
       </c>
       <c r="G38" t="n">
-        <v>87.05185627372239</v>
+        <v>87.04405108272979</v>
       </c>
       <c r="H38" t="n">
-        <v>0.001590004729123962</v>
+        <v>-0.003373509755874693</v>
       </c>
       <c r="I38" t="n">
         <v>70145.01027272303</v>
@@ -1819,16 +1819,16 @@
         <v>1.625178126635585</v>
       </c>
       <c r="E39" t="n">
-        <v>87.8821299983383</v>
+        <v>87.8843082024825</v>
       </c>
       <c r="F39" t="n">
-        <v>1.207063820269667</v>
+        <v>1.216297864697808</v>
       </c>
       <c r="G39" t="n">
-        <v>87.07643890992971</v>
+        <v>87.0661204125232</v>
       </c>
       <c r="H39" t="n">
-        <v>0.02823907181257823</v>
+        <v>0.02535420803478416</v>
       </c>
       <c r="I39" t="n">
         <v>72494.433661744</v>
@@ -1857,16 +1857,16 @@
         <v>4.366388565533375</v>
       </c>
       <c r="E40" t="n">
-        <v>99.3004204240503</v>
+        <v>99.3019109852569</v>
       </c>
       <c r="F40" t="n">
-        <v>12.99273290932742</v>
+        <v>12.99162844460085</v>
       </c>
       <c r="G40" t="n">
-        <v>87.1136053597204</v>
+        <v>87.10625916988209</v>
       </c>
       <c r="H40" t="n">
-        <v>0.04268255598869075</v>
+        <v>0.04610146537909543</v>
       </c>
       <c r="I40" t="n">
         <v>85778.03108882</v>
@@ -1895,16 +1895,16 @@
         <v>3.369502282850756</v>
       </c>
       <c r="E41" t="n">
-        <v>86.8569674821059</v>
+        <v>86.8576893092393</v>
       </c>
       <c r="F41" t="n">
-        <v>-12.53111808470312</v>
+        <v>-12.53170412588047</v>
       </c>
       <c r="G41" t="n">
-        <v>87.1418803697114</v>
+        <v>87.140119344045</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03245762802978902</v>
+        <v>0.03887226301024782</v>
       </c>
       <c r="I41" t="n">
         <v>75009.59663855402</v>
@@ -1933,16 +1933,16 @@
         <v>3.703275695340968</v>
       </c>
       <c r="E42" t="n">
-        <v>89.86535426193799</v>
+        <v>89.8506667692179</v>
       </c>
       <c r="F42" t="n">
-        <v>3.46361019391091</v>
+        <v>3.44584052808807</v>
       </c>
       <c r="G42" t="n">
-        <v>87.12983243635379</v>
+        <v>87.1344075076443</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.01382565226558086</v>
+        <v>-0.006554772295132238</v>
       </c>
       <c r="I42" t="n">
         <v>78594.52182045301</v>
@@ -1971,16 +1971,16 @@
         <v>2.825926258598677</v>
       </c>
       <c r="E43" t="n">
-        <v>88.5968871256878</v>
+        <v>88.5867335968951</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.411519652560301</v>
+        <v>-1.406704276963481</v>
       </c>
       <c r="G43" t="n">
-        <v>87.0673985825769</v>
+        <v>87.0769379178778</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.07165611597210386</v>
+        <v>-0.06595510477471578</v>
       </c>
       <c r="I43" t="n">
         <v>78232.85960185598</v>
@@ -2009,16 +2009,16 @@
         <v>2.54910494362115</v>
       </c>
       <c r="E44" t="n">
-        <v>86.9530168622609</v>
+        <v>86.9394222552001</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.855449233893324</v>
+        <v>-1.859546316710265</v>
       </c>
       <c r="G44" t="n">
-        <v>86.9698575658111</v>
+        <v>86.98206658271179</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1120293225176425</v>
+        <v>-0.1089511613918717</v>
       </c>
       <c r="I44" t="n">
         <v>81140.69622145995</v>
@@ -2047,16 +2047,16 @@
         <v>1.49085798405868</v>
       </c>
       <c r="E45" t="n">
-        <v>83.57876889551621</v>
+        <v>83.60845738628571</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.880541571190918</v>
+        <v>-3.831363014049884</v>
       </c>
       <c r="G45" t="n">
-        <v>86.8750329891906</v>
+        <v>86.88683413262881</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.109031541817501</v>
+        <v>-0.1094851546122158</v>
       </c>
       <c r="I45" t="n">
         <v>80411.97328758003</v>
@@ -2085,16 +2085,16 @@
         <v>1.08928609561989</v>
       </c>
       <c r="E46" t="n">
-        <v>85.6136598750129</v>
+        <v>85.6168073880484</v>
       </c>
       <c r="F46" t="n">
-        <v>2.434698436442105</v>
+        <v>2.402089530827922</v>
       </c>
       <c r="G46" t="n">
-        <v>86.8322247508559</v>
+        <v>86.8408471824996</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.04927565131403355</v>
+        <v>-0.05292740906983795</v>
       </c>
       <c r="I46" t="n">
         <v>77055.77435700996</v>
@@ -2123,16 +2123,16 @@
         <v>0.7386016866142597</v>
       </c>
       <c r="E47" t="n">
-        <v>86.95169321370621</v>
+        <v>86.9508640545</v>
       </c>
       <c r="F47" t="n">
-        <v>1.562873659001028</v>
+        <v>1.558171470240822</v>
       </c>
       <c r="G47" t="n">
-        <v>86.878240836092</v>
+        <v>86.88114429910181</v>
       </c>
       <c r="H47" t="n">
-        <v>0.05299424881503967</v>
+        <v>0.04640341257555747</v>
       </c>
       <c r="I47" t="n">
         <v>89224.28105372799</v>
@@ -2161,16 +2161,16 @@
         <v>0.5695107705871116</v>
       </c>
       <c r="E48" t="n">
-        <v>87.5642974512983</v>
+        <v>87.5722839225151</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7045339946244269</v>
+        <v>0.7146793476665181</v>
       </c>
       <c r="G48" t="n">
-        <v>87.04299045552879</v>
+        <v>87.0383912291917</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1896327755388256</v>
+        <v>0.1809908598217334</v>
       </c>
       <c r="I48" t="n">
         <v>91093.50731224002</v>
@@ -2199,16 +2199,16 @@
         <v>0.7831422501639818</v>
       </c>
       <c r="E49" t="n">
-        <v>87.5171825610971</v>
+        <v>87.5220996686717</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.05380605060801713</v>
+        <v>-0.05730609228805861</v>
       </c>
       <c r="G49" t="n">
-        <v>87.3126703264124</v>
+        <v>87.3022830904637</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3098237657877689</v>
+        <v>0.3031901871636222</v>
       </c>
       <c r="I49" t="n">
         <v>115806.1281151766</v>
@@ -2237,16 +2237,16 @@
         <v>3.988678803798518</v>
       </c>
       <c r="E50" t="n">
-        <v>87.559580871826</v>
+        <v>87.5558948085874</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0484456988766766</v>
+        <v>0.03861326458532233</v>
       </c>
       <c r="G50" t="n">
-        <v>87.6426968361429</v>
+        <v>87.6294124855458</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3779823804457294</v>
+        <v>0.3747088661394145</v>
       </c>
       <c r="I50" t="n">
         <v>98007.58325283098</v>
@@ -2275,16 +2275,16 @@
         <v>-0.9382505348803361</v>
       </c>
       <c r="E51" t="n">
-        <v>87.1605495005782</v>
+        <v>87.1459387169548</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4557255382845256</v>
+        <v>-0.46822214829605</v>
       </c>
       <c r="G51" t="n">
-        <v>87.9987152436936</v>
+        <v>87.983561473938</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4062157149457732</v>
+        <v>0.4041439721516014</v>
       </c>
       <c r="I51" t="n">
         <v>92954.23368112402</v>
@@ -2313,16 +2313,16 @@
         <v>-3.790437448756667</v>
       </c>
       <c r="E52" t="n">
-        <v>89.2959302042992</v>
+        <v>89.3065231935994</v>
       </c>
       <c r="F52" t="n">
-        <v>2.449939469125113</v>
+        <v>2.479271562685284</v>
       </c>
       <c r="G52" t="n">
-        <v>88.35549460774421</v>
+        <v>88.3369131989456</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4054370146911594</v>
+        <v>0.4016110726687003</v>
       </c>
       <c r="I52" t="n">
         <v>107225.884489781</v>
@@ -2351,16 +2351,16 @@
         <v>-2.617016393351357</v>
       </c>
       <c r="E53" t="n">
-        <v>89.6164967616064</v>
+        <v>89.59961486893749</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3589934687659166</v>
+        <v>0.3281861893813982</v>
       </c>
       <c r="G53" t="n">
-        <v>88.6982348336324</v>
+        <v>88.6770190569402</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3879104829980236</v>
+        <v>0.3850098964049522</v>
       </c>
       <c r="I53" t="n">
         <v>106870.185886094</v>
@@ -2389,16 +2389,16 @@
         <v>-2.630093067041417</v>
       </c>
       <c r="E54" t="n">
-        <v>88.68590560553839</v>
+        <v>88.6942393233587</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.038415012521099</v>
+        <v>-1.010468121881033</v>
       </c>
       <c r="G54" t="n">
-        <v>89.02997477815821</v>
+        <v>89.0081343069038</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3740096351951649</v>
+        <v>0.3733946556672123</v>
       </c>
       <c r="I54" t="n">
         <v>110604.694564798</v>
@@ -2427,16 +2427,16 @@
         <v>-2.046341371598492</v>
       </c>
       <c r="E55" t="n">
-        <v>88.5878365496813</v>
+        <v>88.5629651980021</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1105802045854887</v>
+        <v>-0.1480074989740956</v>
       </c>
       <c r="G55" t="n">
-        <v>89.3686892966477</v>
+        <v>89.34922341672829</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3804499769133827</v>
+        <v>0.383211166575407</v>
       </c>
       <c r="I55" t="n">
         <v>116287.8929561601</v>
@@ -2465,16 +2465,16 @@
         <v>-1.171405206831932</v>
       </c>
       <c r="E56" t="n">
-        <v>89.0605674911981</v>
+        <v>89.0573345455982</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5336296267396676</v>
+        <v>0.5582122803711655</v>
       </c>
       <c r="G56" t="n">
-        <v>89.7165138492462</v>
+        <v>89.7013440201069</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3892018058404574</v>
+        <v>0.3940947552910359</v>
       </c>
       <c r="I56" t="n">
         <v>125658.55253241</v>
@@ -2503,16 +2503,16 @@
         <v>-0.4895654752894107</v>
       </c>
       <c r="E57" t="n">
-        <v>89.479497736761</v>
+        <v>89.5038290841354</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4703880262208173</v>
+        <v>0.5013562788684283</v>
       </c>
       <c r="G57" t="n">
-        <v>90.0824355958401</v>
+        <v>90.0745156451564</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4078644286254303</v>
+        <v>0.4160156451678603</v>
       </c>
       <c r="I57" t="n">
         <v>124840.319962399</v>
@@ -2541,16 +2541,16 @@
         <v>0.1859377567481335</v>
       </c>
       <c r="E58" t="n">
-        <v>90.82033754690779</v>
+        <v>90.82844327275509</v>
       </c>
       <c r="F58" t="n">
-        <v>1.49848830632844</v>
+        <v>1.479952536303813</v>
       </c>
       <c r="G58" t="n">
-        <v>90.4546426866625</v>
+        <v>90.45628464308621</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4131849770273988</v>
+        <v>0.423836859066526</v>
       </c>
       <c r="I58" t="n">
         <v>123002.252429758</v>
@@ -2579,16 +2579,16 @@
         <v>0.7113667723696704</v>
       </c>
       <c r="E59" t="n">
-        <v>91.3983467718122</v>
+        <v>91.3931333946762</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6364314871719898</v>
+        <v>0.6217106685681699</v>
       </c>
       <c r="G59" t="n">
-        <v>90.80450859548159</v>
+        <v>90.81487687210441</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3867860160932111</v>
+        <v>0.3964259978542088</v>
       </c>
       <c r="I59" t="n">
         <v>140487.4872662501</v>
@@ -2617,16 +2617,16 @@
         <v>1.034837729849802</v>
       </c>
       <c r="E60" t="n">
-        <v>91.6199224269217</v>
+        <v>91.63118650170929</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2424285153238941</v>
+        <v>0.2604715454990156</v>
       </c>
       <c r="G60" t="n">
-        <v>91.0925767727106</v>
+        <v>91.1087541462234</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3172399495186937</v>
+        <v>0.323600366196473</v>
       </c>
       <c r="I60" t="n">
         <v>141701.960658651</v>
@@ -2655,16 +2655,16 @@
         <v>1.500430024088018</v>
       </c>
       <c r="E61" t="n">
-        <v>91.9509990802339</v>
+        <v>91.94324483655581</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3613588011671425</v>
+        <v>0.3405590899346294</v>
       </c>
       <c r="G61" t="n">
-        <v>91.28528280569969</v>
+        <v>91.30055698403901</v>
       </c>
       <c r="H61" t="n">
-        <v>0.211549656202962</v>
+        <v>0.2105207557857369</v>
       </c>
       <c r="I61" t="n">
         <v>183983.1518799231</v>
@@ -2693,16 +2693,16 @@
         <v>4.275633541163004</v>
       </c>
       <c r="E62" t="n">
-        <v>91.56604933695441</v>
+        <v>91.5845414557251</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4186466130113473</v>
+        <v>-0.3901356553908499</v>
       </c>
       <c r="G62" t="n">
-        <v>91.3651660694297</v>
+        <v>91.3751767984625</v>
       </c>
       <c r="H62" t="n">
-        <v>0.08750946623021605</v>
+        <v>0.08172985673739674</v>
       </c>
       <c r="I62" t="n">
         <v>154517.094181968</v>
@@ -2731,16 +2731,16 @@
         <v>5.401259938031244</v>
       </c>
       <c r="E63" t="n">
-        <v>92.81192979207739</v>
+        <v>92.79679743103949</v>
       </c>
       <c r="F63" t="n">
-        <v>1.360635807861783</v>
+        <v>1.323646934346925</v>
       </c>
       <c r="G63" t="n">
-        <v>91.3282422662988</v>
+        <v>91.33484870999131</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.04041343623548244</v>
+        <v>-0.04413462155061154</v>
       </c>
       <c r="I63" t="n">
         <v>152202.573390117</v>
@@ -2769,16 +2769,16 @@
         <v>3.516929634552102</v>
       </c>
       <c r="E64" t="n">
-        <v>89.70925773950439</v>
+        <v>89.7150797485851</v>
       </c>
       <c r="F64" t="n">
-        <v>-3.342966857303566</v>
+        <v>-3.320931074959262</v>
       </c>
       <c r="G64" t="n">
-        <v>91.1945686185696</v>
+        <v>91.201936319976</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.1463661671484147</v>
+        <v>-0.1455221001540536</v>
       </c>
       <c r="I64" t="n">
         <v>168982.5022787931</v>
@@ -2807,16 +2807,16 @@
         <v>3.429078351259962</v>
       </c>
       <c r="E65" t="n">
-        <v>89.2702705125877</v>
+        <v>89.2618193613056</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4893443976444587</v>
+        <v>-0.5052220747612353</v>
       </c>
       <c r="G65" t="n">
-        <v>91.00246830990029</v>
+        <v>91.0157678836427</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2106488484778026</v>
+        <v>-0.2041277234291954</v>
       </c>
       <c r="I65" t="n">
         <v>177192.288724045</v>
@@ -2845,16 +2845,16 @@
         <v>2.637735424960153</v>
       </c>
       <c r="E66" t="n">
-        <v>90.5473776564022</v>
+        <v>90.53894647205379</v>
       </c>
       <c r="F66" t="n">
-        <v>1.430607453614058</v>
+        <v>1.43076526995128</v>
       </c>
       <c r="G66" t="n">
-        <v>90.79890852624121</v>
+        <v>90.8218198791814</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2236860026322347</v>
+        <v>-0.213092751916605</v>
       </c>
       <c r="I66" t="n">
         <v>179641.5687331929</v>
@@ -2883,16 +2883,16 @@
         <v>2.526190073805856</v>
       </c>
       <c r="E67" t="n">
-        <v>90.6478905104899</v>
+        <v>90.61237084007</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1110058145130495</v>
+        <v>0.08109699844902707</v>
       </c>
       <c r="G67" t="n">
-        <v>90.6452562224659</v>
+        <v>90.67833300471681</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1692226330351758</v>
+        <v>-0.1579872266989071</v>
       </c>
       <c r="I67" t="n">
         <v>196114.524816932</v>
@@ -2921,16 +2921,16 @@
         <v>2.937233031832331</v>
       </c>
       <c r="E68" t="n">
-        <v>93.4888891434523</v>
+        <v>93.4811399848431</v>
       </c>
       <c r="F68" t="n">
-        <v>3.134103415935115</v>
+        <v>3.165979565678128</v>
       </c>
       <c r="G68" t="n">
-        <v>90.6120013953916</v>
+        <v>90.6510628981035</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.03668678148218874</v>
+        <v>-0.03007345383365134</v>
       </c>
       <c r="I68" t="n">
         <v>228215.3447311971</v>
@@ -2959,16 +2959,16 @@
         <v>2.536376195882584</v>
       </c>
       <c r="E69" t="n">
-        <v>89.3962213711394</v>
+        <v>89.43658247493229</v>
       </c>
       <c r="F69" t="n">
-        <v>-4.377704997684788</v>
+        <v>-4.326602682173728</v>
       </c>
       <c r="G69" t="n">
-        <v>90.7426853624724</v>
+        <v>90.77947080988881</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1442236845763318</v>
+        <v>0.141650751441972</v>
       </c>
       <c r="I69" t="n">
         <v>225508.1091356019</v>
@@ -2997,16 +2997,16 @@
         <v>2.345430813057314</v>
       </c>
       <c r="E70" t="n">
-        <v>91.4720232627088</v>
+        <v>91.46972949580019</v>
       </c>
       <c r="F70" t="n">
-        <v>2.322024197143023</v>
+        <v>2.273283442418844</v>
       </c>
       <c r="G70" t="n">
-        <v>91.0526934978253</v>
+        <v>91.0806553800721</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3416342971497528</v>
+        <v>0.3317760805348087</v>
       </c>
       <c r="I70" t="n">
         <v>232153.1572245599</v>
@@ -3035,16 +3035,16 @@
         <v>1.930017682368734</v>
       </c>
       <c r="E71" t="n">
-        <v>90.95580672986959</v>
+        <v>90.9768594453339</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.5643436259812802</v>
+        <v>-0.5388340527331792</v>
       </c>
       <c r="G71" t="n">
-        <v>91.5189428976044</v>
+        <v>91.5366198525703</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5120654665644224</v>
+        <v>0.5006161523492381</v>
       </c>
       <c r="I71" t="n">
         <v>265665.6888902528</v>
@@ -3073,16 +3073,16 @@
         <v>1.978577866854425</v>
       </c>
       <c r="E72" t="n">
-        <v>92.7966021818157</v>
+        <v>92.7911050711152</v>
       </c>
       <c r="F72" t="n">
-        <v>2.023835000895644</v>
+        <v>1.994183616407909</v>
       </c>
       <c r="G72" t="n">
-        <v>92.0700476356418</v>
+        <v>92.079313615738</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6021755940232083</v>
+        <v>0.5928706609898597</v>
       </c>
       <c r="I72" t="n">
         <v>284786.453144324</v>
@@ -3111,16 +3111,16 @@
         <v>1.556466097246845</v>
       </c>
       <c r="E73" t="n">
-        <v>88.2833607868524</v>
+        <v>88.293621364944</v>
       </c>
       <c r="F73" t="n">
-        <v>-4.863584752942302</v>
+        <v>-4.846890984566159</v>
       </c>
       <c r="G73" t="n">
-        <v>92.5990329428498</v>
+        <v>92.6046152410098</v>
       </c>
       <c r="H73" t="n">
-        <v>0.5745465770816196</v>
+        <v>0.5704882070081112</v>
       </c>
       <c r="I73" t="n">
         <v>359667.612326173</v>
@@ -3149,16 +3149,16 @@
         <v>0.8021665104237297</v>
       </c>
       <c r="E74" t="n">
-        <v>94.1147215092931</v>
+        <v>94.1224651159894</v>
       </c>
       <c r="F74" t="n">
-        <v>6.605277223779126</v>
+        <v>6.601658943122317</v>
       </c>
       <c r="G74" t="n">
-        <v>93.0014582056309</v>
+        <v>93.0066148224266</v>
       </c>
       <c r="H74" t="n">
-        <v>0.4345890556216432</v>
+        <v>0.434103181974848</v>
       </c>
       <c r="I74" t="n">
         <v>316578.3876306558</v>
@@ -3187,16 +3187,16 @@
         <v>0.891958310599783</v>
       </c>
       <c r="E75" t="n">
-        <v>93.65305867265489</v>
+        <v>93.6405600911751</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.490532011607371</v>
+        <v>-0.5119978787428039</v>
       </c>
       <c r="G75" t="n">
-        <v>93.2071073233305</v>
+        <v>93.21116442082391</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2211246163956986</v>
+        <v>0.2199301617286551</v>
       </c>
       <c r="I75" t="n">
         <v>318416.9980023959</v>
@@ -3225,16 +3225,16 @@
         <v>1.870009044960996</v>
       </c>
       <c r="E76" t="n">
-        <v>92.86059747327231</v>
+        <v>92.8494357615083</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.8461669171451973</v>
+        <v>-0.8448521974841867</v>
       </c>
       <c r="G76" t="n">
-        <v>93.2126823080966</v>
+        <v>93.2169989063562</v>
       </c>
       <c r="H76" t="n">
-        <v>0.005981287185278461</v>
+        <v>0.006259427793381178</v>
       </c>
       <c r="I76" t="n">
         <v>363148.3390793051</v>
@@ -3263,16 +3263,16 @@
         <v>2.251038696324659</v>
       </c>
       <c r="E77" t="n">
-        <v>92.2413449481005</v>
+        <v>92.2346652893996</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.6668625251415534</v>
+        <v>-0.6621154636715261</v>
       </c>
       <c r="G77" t="n">
-        <v>93.07467686117199</v>
+        <v>93.0828849110782</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.1480543671819845</v>
+        <v>-0.1438728953425397</v>
       </c>
       <c r="I77" t="n">
         <v>385814.0669280695</v>
@@ -3301,16 +3301,16 @@
         <v>1.865923539614944</v>
       </c>
       <c r="E78" t="n">
-        <v>90.7756102651382</v>
+        <v>90.7744745048022</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.589021369741516</v>
+        <v>-1.58312580201364</v>
       </c>
       <c r="G78" t="n">
-        <v>92.8525689642105</v>
+        <v>92.8688935767515</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.2386340779810325</v>
+        <v>-0.2298933198419064</v>
       </c>
       <c r="I78" t="n">
         <v>388897.17588154</v>
@@ -3339,16 +3339,16 @@
         <v>1.403608626528108</v>
       </c>
       <c r="E79" t="n">
-        <v>90.0543805475256</v>
+        <v>89.98395152912251</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.7945192717581619</v>
+        <v>-0.8708648328642994</v>
       </c>
       <c r="G79" t="n">
-        <v>92.5611413334091</v>
+        <v>92.5901237017046</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.3138606007915001</v>
+        <v>-0.3001757254882307</v>
       </c>
       <c r="I79" t="n">
         <v>425805.7399507801</v>
@@ -3377,16 +3377,16 @@
         <v>0.8156724923206848</v>
       </c>
       <c r="E80" t="n">
-        <v>91.97335920176511</v>
+        <v>91.9681178599114</v>
       </c>
       <c r="F80" t="n">
-        <v>2.130910947998558</v>
+        <v>2.205022447971444</v>
       </c>
       <c r="G80" t="n">
-        <v>92.147831619844</v>
+        <v>92.1898704653613</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.44652616379949</v>
+        <v>-0.4322850217079264</v>
       </c>
       <c r="I80" t="n">
         <v>482669.38905065</v>
@@ -3415,16 +3415,16 @@
         <v>1.347221062010928</v>
       </c>
       <c r="E81" t="n">
-        <v>93.5226904821095</v>
+        <v>93.58524965695609</v>
       </c>
       <c r="F81" t="n">
-        <v>1.684543539336829</v>
+        <v>1.758361304629446</v>
       </c>
       <c r="G81" t="n">
-        <v>91.5085948427721</v>
+        <v>91.5591264831822</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.6937078885470385</v>
+        <v>-0.6841792693656998</v>
       </c>
       <c r="I81" t="n">
         <v>537409.23036958</v>
@@ -3453,16 +3453,16 @@
         <v>1.601978475819399</v>
       </c>
       <c r="E82" t="n">
-        <v>92.55193514234711</v>
+        <v>92.5856537509847</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.037989106983716</v>
+        <v>-1.068112666937878</v>
       </c>
       <c r="G82" t="n">
-        <v>90.52840464401589</v>
+        <v>90.5793456225402</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.071145503261576</v>
+        <v>-1.070107261040732</v>
       </c>
       <c r="I82" t="n">
         <v>580113.0483323103</v>
@@ -3491,16 +3491,16 @@
         <v>2.172403856952654</v>
       </c>
       <c r="E83" t="n">
-        <v>99.92539534215091</v>
+        <v>99.938235533922</v>
       </c>
       <c r="F83" t="n">
-        <v>7.966835256835253</v>
+        <v>7.941383448792777</v>
       </c>
       <c r="G83" t="n">
-        <v>89.1609161361733</v>
+        <v>89.2034416509328</v>
       </c>
       <c r="H83" t="n">
-        <v>-1.510562914722698</v>
+        <v>-1.519004097624006</v>
       </c>
       <c r="I83" t="n">
         <v>708384.3504217999</v>
@@ -3529,16 +3529,16 @@
         <v>1.806934260448601</v>
       </c>
       <c r="E84" t="n">
-        <v>91.5680775952508</v>
+        <v>91.552333710361</v>
       </c>
       <c r="F84" t="n">
-        <v>-8.363557350245273</v>
+        <v>-8.391084532120416</v>
       </c>
       <c r="G84" t="n">
-        <v>87.4670014953694</v>
+        <v>87.4961433465707</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.899839878514513</v>
+        <v>-1.91393770550134</v>
       </c>
       <c r="I84" t="n">
         <v>764304.8156269495</v>
@@ -3567,16 +3567,16 @@
         <v>0.9389117587374818</v>
       </c>
       <c r="E85" t="n">
-        <v>82.1034778402306</v>
+        <v>82.11158971459329</v>
       </c>
       <c r="F85" t="n">
-        <v>-10.3361346045241</v>
+        <v>-10.31185510315321</v>
       </c>
       <c r="G85" t="n">
-        <v>85.6287781711613</v>
+        <v>85.6427548930222</v>
       </c>
       <c r="H85" t="n">
-        <v>-2.101619231002701</v>
+        <v>-2.118251596767266</v>
       </c>
       <c r="I85" t="n">
         <v>1147057.74707415</v>
@@ -3605,16 +3605,16 @@
         <v>-13.86973843268604</v>
       </c>
       <c r="E86" t="n">
-        <v>81.0212371120664</v>
+        <v>81.0402943604514</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.318142369401428</v>
+        <v>-1.304682271851689</v>
       </c>
       <c r="G86" t="n">
-        <v>83.90058704587339</v>
+        <v>83.8996112681381</v>
       </c>
       <c r="H86" t="n">
-        <v>-2.018236347870655</v>
+        <v>-2.035366128823725</v>
       </c>
       <c r="I86" t="n">
         <v>1101738.03986254</v>
@@ -3643,16 +3643,16 @@
         <v>-12.66925721950585</v>
       </c>
       <c r="E87" t="n">
-        <v>80.5562800740435</v>
+        <v>80.54882438067131</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.5738705734396348</v>
+        <v>-0.6064513754036227</v>
       </c>
       <c r="G87" t="n">
-        <v>82.5111546027625</v>
+        <v>82.4942897237147</v>
       </c>
       <c r="H87" t="n">
-        <v>-1.656046151800112</v>
+        <v>-1.675003642069427</v>
       </c>
       <c r="I87" t="n">
         <v>1193012.006769949</v>
@@ -3681,16 +3681,16 @@
         <v>-11.53375325157015</v>
       </c>
       <c r="E88" t="n">
-        <v>80.26107713714011</v>
+        <v>80.243478713656</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.3664555223156469</v>
+        <v>-0.3790814693610542</v>
       </c>
       <c r="G88" t="n">
-        <v>81.5874513868041</v>
+        <v>81.55266466127701</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.119488898689426</v>
+        <v>-1.141442717540002</v>
       </c>
       <c r="I88" t="n">
         <v>1422932.96311051</v>
@@ -3719,16 +3719,16 @@
         <v>-13.03401275473249</v>
       </c>
       <c r="E89" t="n">
-        <v>80.5260346478279</v>
+        <v>80.51298970138311</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3301195550055525</v>
+        <v>0.3358665302744868</v>
       </c>
       <c r="G89" t="n">
-        <v>81.1328595031441</v>
+        <v>81.0801134543822</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.5571835814613024</v>
+        <v>-0.5794430002471529</v>
       </c>
       <c r="I89" t="n">
         <v>1335118.1618885</v>
@@ -3757,16 +3757,16 @@
         <v>-12.41589874551638</v>
       </c>
       <c r="E90" t="n">
-        <v>81.0456490396727</v>
+        <v>81.0155854857821</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6452750270360212</v>
+        <v>0.6242418599322548</v>
       </c>
       <c r="G90" t="n">
-        <v>81.0539897978079</v>
+        <v>80.9875992865167</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.09721055786668842</v>
+        <v>-0.1141021687365509</v>
       </c>
       <c r="I90" t="n">
         <v>1412879.732691079</v>
@@ -3795,16 +3795,16 @@
         <v>-11.59299445253313</v>
       </c>
       <c r="E91" t="n">
-        <v>81.2232694879514</v>
+        <v>81.1566754421986</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2191609918402264</v>
+        <v>0.174151622271836</v>
       </c>
       <c r="G91" t="n">
-        <v>81.2017050087473</v>
+        <v>81.12937846021281</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1822429855802028</v>
+        <v>0.1750628181908667</v>
       </c>
       <c r="I91" t="n">
         <v>1532919.328725981</v>
@@ -3833,16 +3833,16 @@
         <v>-11.69843127842053</v>
       </c>
       <c r="E92" t="n">
-        <v>82.69715433105191</v>
+        <v>82.65450034565259</v>
       </c>
       <c r="F92" t="n">
-        <v>1.814609104499468</v>
+        <v>1.845596674941135</v>
       </c>
       <c r="G92" t="n">
-        <v>81.4411452574671</v>
+        <v>81.3720689602512</v>
       </c>
       <c r="H92" t="n">
-        <v>0.2948709620001324</v>
+        <v>0.2991400952953285</v>
       </c>
       <c r="I92" t="n">
         <v>1588377.398849001</v>
@@ -3871,16 +3871,16 @@
         <v>-11.4938805021935</v>
       </c>
       <c r="E93" t="n">
-        <v>82.4532626530677</v>
+        <v>82.5755988810259</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.2949214878759534</v>
+        <v>-0.09545936917740505</v>
       </c>
       <c r="G93" t="n">
-        <v>81.7131454422844</v>
+        <v>81.6543725200619</v>
       </c>
       <c r="H93" t="n">
-        <v>0.333983742440509</v>
+        <v>0.3469293129914064</v>
       </c>
       <c r="I93" t="n">
         <v>1668468.303919509</v>
@@ -3909,16 +3909,16 @@
         <v>-11.63416259782897</v>
       </c>
       <c r="E94" t="n">
-        <v>82.82830925128729</v>
+        <v>82.8827368277383</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4548596212592031</v>
+        <v>0.3719475860598038</v>
       </c>
       <c r="G94" t="n">
-        <v>82.025734861937</v>
+        <v>81.98051272906611</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3825448377499754</v>
+        <v>0.3994154861995725</v>
       </c>
       <c r="I94" t="n">
         <v>1585125.58840589</v>
@@ -3947,16 +3947,16 @@
         <v>-12.29866765668779</v>
       </c>
       <c r="E95" t="n">
-        <v>81.54562146231051</v>
+        <v>81.5645347354468</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.548610373157956</v>
+        <v>-1.590442283573751</v>
       </c>
       <c r="G95" t="n">
-        <v>82.4079269536917</v>
+        <v>82.3759413816136</v>
       </c>
       <c r="H95" t="n">
-        <v>0.4659416857380165</v>
+        <v>0.482344693127672</v>
       </c>
       <c r="I95" t="n">
         <v>1698369.96171217</v>
@@ -3985,16 +3985,16 @@
         <v>-11.87089129884695</v>
       </c>
       <c r="E96" t="n">
-        <v>83.08961396821481</v>
+        <v>83.0540957080719</v>
       </c>
       <c r="F96" t="n">
-        <v>1.893409453771739</v>
+        <v>1.826236093243793</v>
       </c>
       <c r="G96" t="n">
-        <v>82.8819216505357</v>
+        <v>82.85881610783559</v>
       </c>
       <c r="H96" t="n">
-        <v>0.5751809496559162</v>
+        <v>0.586184167516862</v>
       </c>
       <c r="I96" t="n">
         <v>1824221.77378981</v>
@@ -4003,7 +4003,7 @@
         <v>23282.69425171925</v>
       </c>
       <c r="K96" t="n">
-        <v>138.6772576191901</v>
+        <v>138.6772576191902</v>
       </c>
       <c r="L96" t="n">
         <v>-7.648521125656984</v>
@@ -4017,22 +4017,22 @@
         <v>101.7789566356381</v>
       </c>
       <c r="C97" t="n">
-        <v>-3.254552772957686</v>
+        <v>-3.254552772957631</v>
       </c>
       <c r="D97" t="n">
         <v>-11.04822005628372</v>
       </c>
       <c r="E97" t="n">
-        <v>82.1606031425932</v>
+        <v>82.1781550510152</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.118082972412154</v>
+        <v>-1.054662806919922</v>
       </c>
       <c r="G97" t="n">
-        <v>83.4293186293864</v>
+        <v>83.4084028573247</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6604540145180806</v>
+        <v>0.6632809582674497</v>
       </c>
       <c r="I97" t="n">
         <v>2228212.726127959</v>
@@ -4044,7 +4044,7 @@
         <v>94.2546250885413</v>
       </c>
       <c r="L97" t="n">
-        <v>-3.25455277295768</v>
+        <v>-3.254552772957652</v>
       </c>
     </row>
     <row r="98">
@@ -4061,16 +4061,16 @@
         <v>4.18041907640152</v>
       </c>
       <c r="E98" t="n">
-        <v>83.8438755606705</v>
+        <v>83.84362213630899</v>
       </c>
       <c r="F98" t="n">
-        <v>2.048758594378739</v>
+        <v>2.026654266282677</v>
       </c>
       <c r="G98" t="n">
-        <v>83.9638707238889</v>
+        <v>83.93687023363719</v>
       </c>
       <c r="H98" t="n">
-        <v>0.6407245118195419</v>
+        <v>0.6335900918957407</v>
       </c>
       <c r="I98" t="n">
         <v>1870036.186891431</v>
@@ -4082,7 +4082,7 @@
         <v>69.73510210510199</v>
       </c>
       <c r="L98" t="n">
-        <v>4.18041907640152</v>
+        <v>4.180419076401492</v>
       </c>
     </row>
     <row r="99">
@@ -4099,16 +4099,16 @@
         <v>2.76900165398819</v>
       </c>
       <c r="E99" t="n">
-        <v>84.1931758552184</v>
+        <v>84.18566384028</v>
       </c>
       <c r="F99" t="n">
-        <v>0.416608001731916</v>
+        <v>0.4079519649269514</v>
       </c>
       <c r="G99" t="n">
-        <v>84.3739056105687</v>
+        <v>84.3410558272426</v>
       </c>
       <c r="H99" t="n">
-        <v>0.4883468129145427</v>
+        <v>0.4815352210302279</v>
       </c>
       <c r="I99" t="n">
         <v>1792366.127568839</v>
@@ -4131,22 +4131,22 @@
         <v>86.79581994352243</v>
       </c>
       <c r="C100" t="n">
-        <v>2.99867840415291</v>
+        <v>2.998678404152888</v>
       </c>
       <c r="D100" t="n">
-        <v>2.848935040838207</v>
+        <v>2.848935040838185</v>
       </c>
       <c r="E100" t="n">
-        <v>85.2008742968205</v>
+        <v>85.19922544504639</v>
       </c>
       <c r="F100" t="n">
-        <v>1.196888502382862</v>
+        <v>1.203959865054173</v>
       </c>
       <c r="G100" t="n">
-        <v>84.56638171137951</v>
+        <v>84.52732122477509</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2281227820591738</v>
+        <v>0.2208478370415747</v>
       </c>
       <c r="I100" t="n">
         <v>2045404.050644631</v>
@@ -4172,19 +4172,19 @@
         <v>8.899932079157956</v>
       </c>
       <c r="D101" t="n">
-        <v>4.278109066209712</v>
+        <v>4.27810906620969</v>
       </c>
       <c r="E101" t="n">
-        <v>84.5268007617111</v>
+        <v>84.4931832971489</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.7911580023945248</v>
+        <v>-0.828695500703688</v>
       </c>
       <c r="G101" t="n">
-        <v>84.49662070230779</v>
+        <v>84.4402402386811</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.08249260245023038</v>
+        <v>-0.1030211117922732</v>
       </c>
       <c r="I101" t="n">
         <v>1975378.38408263</v>
@@ -4210,19 +4210,19 @@
         <v>6.052980488471715</v>
       </c>
       <c r="D102" t="n">
-        <v>4.622927214511807</v>
+        <v>4.622927214511785</v>
       </c>
       <c r="E102" t="n">
-        <v>84.14290630360431</v>
+        <v>84.1067835515469</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.4541689199725312</v>
+        <v>-0.457314697498262</v>
       </c>
       <c r="G102" t="n">
-        <v>84.1865520768514</v>
+        <v>84.10060796179231</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.3669597942251528</v>
+        <v>-0.4022161423614818</v>
       </c>
       <c r="I102" t="n">
         <v>1987424.31025721</v>
@@ -4231,7 +4231,7 @@
         <v>22290.8495941882</v>
       </c>
       <c r="K102" t="n">
-        <v>40.66479009305408</v>
+        <v>40.66479009305411</v>
       </c>
       <c r="L102" t="n">
         <v>6.052980488471718</v>
@@ -4245,22 +4245,22 @@
         <v>81.21856762481966</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7554482396138873</v>
+        <v>0.7554482396138651</v>
       </c>
       <c r="D103" t="n">
-        <v>3.965290325654069</v>
+        <v>3.965290325654047</v>
       </c>
       <c r="E103" t="n">
-        <v>84.1683919228347</v>
+        <v>84.0695294315566</v>
       </c>
       <c r="F103" t="n">
-        <v>0.03028849412265799</v>
+        <v>-0.04429383507152806</v>
       </c>
       <c r="G103" t="n">
-        <v>83.7281514712783</v>
+        <v>83.609445620241</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.5445057366818418</v>
+        <v>-0.584017587333534</v>
       </c>
       <c r="I103" t="n">
         <v>2009502.29199285</v>
@@ -4272,7 +4272,7 @@
         <v>31.08989196861128</v>
       </c>
       <c r="L103" t="n">
-        <v>0.7554482396138837</v>
+        <v>0.7554482396138695</v>
       </c>
     </row>
     <row r="104">
@@ -4286,19 +4286,19 @@
         <v>0.9978267674925156</v>
       </c>
       <c r="D104" t="n">
-        <v>3.53153770066994</v>
+        <v>3.531537700669918</v>
       </c>
       <c r="E104" t="n">
-        <v>82.9952694241469</v>
+        <v>82.90065185553669</v>
       </c>
       <c r="F104" t="n">
-        <v>-1.393780339492906</v>
+        <v>-1.39037007096789</v>
       </c>
       <c r="G104" t="n">
-        <v>83.23389109945199</v>
+        <v>83.09347903316809</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.5903156383380264</v>
+        <v>-0.6171151874591487</v>
       </c>
       <c r="I104" t="n">
         <v>2059033.274186821</v>
@@ -4310,7 +4310,7 @@
         <v>29.63123724115408</v>
       </c>
       <c r="L104" t="n">
-        <v>0.9978267674925121</v>
+        <v>0.9978267674925405</v>
       </c>
     </row>
     <row r="105">
@@ -4321,22 +4321,22 @@
         <v>82.55780826244025</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3338471666764153</v>
+        <v>0.3338471666764375</v>
       </c>
       <c r="D105" t="n">
         <v>3.118802083334171</v>
       </c>
       <c r="E105" t="n">
-        <v>82.3814441339273</v>
+        <v>82.5998467196804</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.7395906953234288</v>
+        <v>-0.3628501454735016</v>
       </c>
       <c r="G105" t="n">
-        <v>82.78814025863009</v>
+        <v>82.645116127447</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.5355400726000994</v>
+        <v>-0.5395885584982238</v>
       </c>
       <c r="I105" t="n">
         <v>2106920.638145701</v>
@@ -4348,7 +4348,7 @@
         <v>26.27873320674988</v>
       </c>
       <c r="L105" t="n">
-        <v>0.3338471666764207</v>
+        <v>0.3338471666764349</v>
       </c>
     </row>
     <row r="106">
@@ -4365,16 +4365,16 @@
         <v>2.698161179386305</v>
       </c>
       <c r="E106" t="n">
-        <v>82.4960781781944</v>
+        <v>82.5716976711655</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1391503213766612</v>
+        <v>-0.03407881446855754</v>
       </c>
       <c r="G106" t="n">
-        <v>82.4414494501477</v>
+        <v>82.3185025083117</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.4187686876397123</v>
+        <v>-0.3952001454406968</v>
       </c>
       <c r="I106" t="n">
         <v>1962362.99495929</v>
@@ -4394,25 +4394,25 @@
         <v>45931</v>
       </c>
       <c r="B107" t="n">
-        <v>82.22898274286365</v>
+        <v>82.22898274286368</v>
       </c>
       <c r="C107" t="n">
-        <v>2.730557452574045</v>
+        <v>2.730557452574067</v>
       </c>
       <c r="D107" t="n">
         <v>2.701428422597973</v>
       </c>
       <c r="E107" t="n">
-        <v>83.7196451667082</v>
+        <v>83.7297087031734</v>
       </c>
       <c r="F107" t="n">
-        <v>1.483182007599027</v>
+        <v>1.402430935378845</v>
       </c>
       <c r="G107" t="n">
-        <v>82.2089857490018</v>
+        <v>82.122720060402</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.2819743013937028</v>
+        <v>-0.2378352884759067</v>
       </c>
       <c r="I107" t="n">
         <v>2170966.83765787</v>
@@ -4424,7 +4424,7 @@
         <v>27.82649755941648</v>
       </c>
       <c r="L107" t="n">
-        <v>2.730557452574047</v>
+        <v>2.730557452574061</v>
       </c>
     </row>
     <row r="108">
@@ -4441,16 +4441,16 @@
         <v>2.170819646515598</v>
       </c>
       <c r="E108" t="n">
-        <v>80.734007927542</v>
+        <v>80.70127840395089</v>
       </c>
       <c r="F108" t="n">
-        <v>-3.566232552970106</v>
+        <v>-3.616912498714726</v>
       </c>
       <c r="G108" t="n">
-        <v>82.07272434392441</v>
+        <v>82.02612974990561</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.1657500136218886</v>
+        <v>-0.117617037557153</v>
       </c>
       <c r="I108" t="n">
         <v>2211322.30967165</v>
@@ -4459,7 +4459,7 @@
         <v>22630.11697255106</v>
       </c>
       <c r="K108" t="n">
-        <v>21.22003702859223</v>
+        <v>21.2200370285922</v>
       </c>
       <c r="L108" t="n">
         <v>-2.802842626857966</v>
@@ -4479,16 +4479,16 @@
         <v>1.99995308922194</v>
       </c>
       <c r="E109" t="n">
-        <v>82.7509620873071</v>
+        <v>82.7735131307001</v>
       </c>
       <c r="F109" t="n">
-        <v>2.498270817392466</v>
+        <v>2.567784262817526</v>
       </c>
       <c r="G109" t="n">
-        <v>81.9943179475853</v>
+        <v>81.9731868599506</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.0955328301404279</v>
+        <v>-0.06454393266685088</v>
       </c>
       <c r="I109" t="n">
         <v>2796110.361688118</v>
@@ -4508,37 +4508,37 @@
         <v>46023</v>
       </c>
       <c r="B110" t="n">
-        <v>82.7686979094896</v>
+        <v>82.76869790948962</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.185253935731445</v>
+        <v>-1.185253935731423</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.185253935731445</v>
+        <v>-1.185253935731423</v>
       </c>
       <c r="E110" t="n">
-        <v>81.4535371056478</v>
+        <v>81.4567391316909</v>
       </c>
       <c r="F110" t="n">
-        <v>-1.567866945511099</v>
+        <v>-1.590815647669814</v>
       </c>
       <c r="G110" t="n">
-        <v>81.9503494625544</v>
+        <v>81.93310113236571</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.05362381946881101</v>
+        <v>-0.04890102376205618</v>
       </c>
       <c r="I110" t="n">
         <v>2339233.32491327</v>
       </c>
       <c r="J110" t="n">
-        <v>22759.48130906785</v>
+        <v>22759.48130906786</v>
       </c>
       <c r="K110" t="n">
         <v>25.09027051512771</v>
       </c>
       <c r="L110" t="n">
-        <v>-1.185253935731438</v>
+        <v>-1.18525393573141</v>
       </c>
     </row>
     <row r="111">
@@ -4552,19 +4552,19 @@
         <v>-3.085199632764357</v>
       </c>
       <c r="D111" t="n">
-        <v>-2.104272181592648</v>
+        <v>-2.104272181592626</v>
       </c>
       <c r="E111" t="n">
-        <v>81.6898556535634</v>
+        <v>81.67766785738129</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2901268088690614</v>
+        <v>0.2712221579766805</v>
       </c>
       <c r="G111" t="n">
-        <v>81.9309493399125</v>
+        <v>81.8878722385233</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.02367302002875249</v>
+        <v>-0.05520222378662254</v>
       </c>
       <c r="I111" t="n">
         <v>2213838.94861108</v>
@@ -4573,7 +4573,7 @@
         <v>20913.07775642506</v>
       </c>
       <c r="K111" t="n">
-        <v>23.51488429509246</v>
+        <v>23.51488429509243</v>
       </c>
       <c r="L111" t="n">
         <v>-3.085199632764372</v>
@@ -4590,28 +4590,28 @@
         <v>-5.08699575565058</v>
       </c>
       <c r="D112" t="n">
-        <v>-3.143847692081991</v>
+        <v>-3.14384769208198</v>
       </c>
       <c r="E112" t="n">
-        <v>81.6102466613372</v>
+        <v>81.5792604333452</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.09745272725638188</v>
+        <v>-0.1204826565419665</v>
       </c>
       <c r="G112" t="n">
-        <v>81.91592428929</v>
+        <v>81.8286155386851</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.01833867512038978</v>
+        <v>-0.07236321840869664</v>
       </c>
       <c r="I112" t="n">
-        <v>2463630.474624511</v>
+        <v>2463630.47462451</v>
       </c>
       <c r="J112" t="n">
         <v>22652.74141797432</v>
       </c>
       <c r="K112" t="n">
-        <v>20.44712993738678</v>
+        <v>20.44712993738675</v>
       </c>
       <c r="L112" t="n">
         <v>-5.086995755650577</v>
@@ -4631,25 +4631,25 @@
         <v>-3.280861648671796</v>
       </c>
       <c r="E113" t="n">
-        <v>82.2180180641131</v>
+        <v>82.1759047663616</v>
       </c>
       <c r="F113" t="n">
-        <v>0.7447243791554712</v>
+        <v>0.7313676660551494</v>
       </c>
       <c r="G113" t="n">
-        <v>81.8769058099839</v>
+        <v>81.7482402536461</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.04763234944198302</v>
+        <v>-0.09822393365681137</v>
       </c>
       <c r="I113" t="n">
-        <v>2399630.788437171</v>
+        <v>2399630.78843717</v>
       </c>
       <c r="J113" t="n">
         <v>21591.40605336622</v>
       </c>
       <c r="K113" t="n">
-        <v>21.47701968256399</v>
+        <v>21.47701968256396</v>
       </c>
       <c r="L113" t="n">
         <v>-3.699332482329325</v>
@@ -4669,16 +4669,16 @@
         <v>-2.767451458081505</v>
       </c>
       <c r="E114" t="n">
-        <v>82.85005969098241</v>
+        <v>82.7911217842731</v>
       </c>
       <c r="F114" t="n">
-        <v>0.7687385827963595</v>
+        <v>0.7486586483722419</v>
       </c>
       <c r="G114" t="n">
-        <v>81.80361768625539</v>
+        <v>81.63606230730311</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.0895101286540978</v>
+        <v>-0.1372236833416025</v>
       </c>
       <c r="I114" t="n">
         <v>2502834.183285178</v>
@@ -4707,16 +4707,16 @@
         <v>-2.826546441348532</v>
       </c>
       <c r="E115" t="n">
-        <v>81.7875860354298</v>
+        <v>81.6764400633199</v>
       </c>
       <c r="F115" t="n">
-        <v>-1.282405419519876</v>
+        <v>-1.346378327687958</v>
       </c>
       <c r="G115" t="n">
-        <v>81.6916642200616</v>
+        <v>81.47274480836781</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.1368563755006278</v>
+        <v>-0.2000555812215907</v>
       </c>
       <c r="I115" t="n">
         <v>2484975.474028381</v>
@@ -4728,7 +4728,7 @@
         <v>23.66124109089705</v>
       </c>
       <c r="L115" t="n">
-        <v>-3.126053072586743</v>
+        <v>-3.126053072586728</v>
       </c>
     </row>
     <row r="116">
@@ -4736,37 +4736,75 @@
         <v>46204</v>
       </c>
       <c r="B116" t="n">
-        <v>80.27011296239861</v>
+        <v>80.27011296239863</v>
       </c>
       <c r="C116" t="n">
-        <v>-2.067190707961952</v>
+        <v>-2.067190707961941</v>
       </c>
       <c r="D116" t="n">
         <v>-2.718268157804804</v>
       </c>
       <c r="E116" t="n">
-        <v>81.2363820893659</v>
+        <v>81.09349936250661</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.6739457328219913</v>
+        <v>-0.7137195259261659</v>
       </c>
       <c r="G116" t="n">
-        <v>81.5580284395183</v>
+        <v>81.26314708774839</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.1635855773280781</v>
+        <v>-0.2572611504772624</v>
       </c>
       <c r="I116" t="n">
-        <v>2591042.388567678</v>
+        <v>2591042.388567679</v>
       </c>
       <c r="J116" t="n">
         <v>22072.42812545222</v>
       </c>
       <c r="K116" t="n">
-        <v>25.83781044485379</v>
+        <v>25.83781044485383</v>
       </c>
       <c r="L116" t="n">
-        <v>-2.06719070796197</v>
+        <v>-2.067190707961956</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79.46845968899339</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-3.74204286483264</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-2.846841081167983</v>
+      </c>
+      <c r="E117" t="n">
+        <v>80.452139598576</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-0.790889243863532</v>
+      </c>
+      <c r="G117" t="n">
+        <v>81.0370215793688</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-0.2782632921358896</v>
+      </c>
+      <c r="I117" t="n">
+        <v>2616930.121204408</v>
+      </c>
+      <c r="J117" t="n">
+        <v>21851.99198046935</v>
+      </c>
+      <c r="K117" t="n">
+        <v>24.20639267682934</v>
+      </c>
+      <c r="L117" t="n">
+        <v>-3.742042864832655</v>
       </c>
     </row>
   </sheetData>
@@ -4839,7 +4877,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19T15:37:12Z</t>
+          <t>2026-10-22T22:27:57Z</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4889,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
